--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -4785,23 +4785,23 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>9500000</v>
+        <v>8550000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>27299</v>
+        <v>24569</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="5" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -21023,23 +21023,23 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
-        <v>8243000</v>
+        <v>7418700</v>
       </c>
       <c r="I323" s="5" t="n">
-        <v>23687</v>
+        <v>21318</v>
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K323" s="5" t="n">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N323" s="3" t="inlineStr">
@@ -26418,7 +26418,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27810,12 +27810,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>H | 348呎 (2房)
-$950万
-$27,299/呎
-(在售)</t>
+$855万
+$24,569/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -28244,7 +28244,7 @@
           <t>P | 273呎 (1房)
 $603万
 $22,095/呎
-(26年-08月-14日)</t>
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="P12" s="23" t="inlineStr">
@@ -29953,12 +29953,12 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>F | 348呎 (2房)
-$824万
-$23,687/呎
-(在售)</t>
+$742万
+$21,318/呎
+(26年-09月-06日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -30752,7 +30752,7 @@
           <t>K | 357呎 (3房)
 $1178万
 $33,000/呎
-(26年-08月-17日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="L32" s="20" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -2308,7 +2308,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -26965,38 +26965,30 @@
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H416" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I416" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>8732000</v>
+      </c>
+      <c r="I416" s="5" t="n">
+        <v>24323</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K416" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L416" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K416" s="5" t="n">
+        <v>8732000</v>
+      </c>
+      <c r="L416" s="5" t="n">
+        <v>24323</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
@@ -27005,7 +26997,7 @@
       </c>
       <c r="N416" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -27162,7 +27154,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27172,7 +27164,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27386,7 +27378,7 @@
           <t>B | 397呎 (3房)
 $1017万
 $25,613/呎
-(26年-08月-27日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -27545,7 +27537,7 @@
           <t>F | 348呎 (2房)
 $862万
 $24,784/呎
-(26年-08月-26日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -27680,7 +27672,7 @@
           <t>G | 348呎 (2房)
 $858万
 $24,652/呎
-(26年-08月-16日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -28577,7 +28569,7 @@
           <t>H | 348呎 (2房)
 $830万
 $23,848/呎
-(26年-08月-22日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
@@ -29537,7 +29529,7 @@
           <t>A | 512呎 (3房)
 $1156万
 $22,584/呎
-(26年-08月-17日)</t>
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -29545,7 +29537,7 @@
           <t>B | 397呎 (3房)
 $874万
 $22,022/呎
-(26年-08月-26日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -30172,7 +30164,7 @@
           <t>A | 512呎 (3房)
 $1081万
 $21,117/呎
-(26年-08月-16日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -30683,12 +30675,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 359呎 (3房)
-招标单位
--
-(在售)</t>
+$873万
+$24,323/呎
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -23262,14 +23262,14 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
-        <v>10811700</v>
+        <v>10991800</v>
       </c>
       <c r="I358" s="5" t="n">
-        <v>21117</v>
+        <v>21468</v>
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
@@ -23277,10 +23277,10 @@
         </is>
       </c>
       <c r="K358" s="5" t="n">
-        <v>10811700</v>
+        <v>10991800</v>
       </c>
       <c r="L358" s="5" t="n">
-        <v>21117</v>
+        <v>21468</v>
       </c>
       <c r="M358" s="3" t="inlineStr">
         <is>
@@ -30162,9 +30162,9 @@
       <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1081万
-$21,117/呎
-(26年-09月-09日)</t>
+$1099万
+$21,468/呎
+(26年-08月-16日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -21028,7 +21028,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -29950,7 +29950,7 @@
           <t>F | 348呎 (2房)
 $742万
 $21,318/呎
-(26年-09月-06日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -11512,7 +11512,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -28680,7 +28680,7 @@
           <t>F | 348呎 (2房)
 $819万
 $23,537/呎
-(26年-08月-30日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -27807,7 +27807,7 @@
           <t>H | 348呎 (2房)
 $855万
 $24,569/呎
-(26年-09月-05日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -15477,23 +15477,23 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
-        <v>8934000</v>
+        <v>8040600</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>25526</v>
+        <v>22973</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K236" s="5" t="n">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
@@ -26970,7 +26970,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27164,7 +27164,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -29159,12 +29159,12 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
-$893万
-$25,526/呎
-(在售)</t>
+$804万
+$22,973/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -30680,7 +30680,7 @@
           <t>B | 359呎 (3房)
 $873万
 $24,323/呎
-(26年-09月-08日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -15601,23 +15601,23 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
-        <v>13330000</v>
+        <v>11997000</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>26035</v>
+        <v>23432</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K238" s="5" t="n">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27164,7 +27164,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -29143,12 +29143,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 512呎 (3房)
-$1333万
-$26,035/呎
-(在售)</t>
+$1200万
+$23,432/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -4847,23 +4847,23 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>9479000</v>
+        <v>8531100</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>27239</v>
+        <v>24515</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27164,7 +27164,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27794,12 +27794,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>G | 348呎 (2房)
-$948万
-$27,239/呎
-(在售)</t>
+$853万
+$24,515/呎
+(26年-10月-18日)</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -29164,7 +29164,7 @@
           <t>C | 350呎 (2房)
 $804万
 $22,973/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">

--- a/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
+++ b/九龙-马头角-壹沐第2期/壹沐第2期_销控明细表.xlsx
@@ -4154,14 +4154,14 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>8113300</v>
+        <v>8423600</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>23181</v>
+        <v>24067</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>8113300</v>
+        <v>8423600</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>23181</v>
+        <v>24067</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -5669,34 +5669,34 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>12992000</v>
+        <v>12472300</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>28000</v>
+        <v>26880</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="5" t="n">
-        <v>11692800</v>
+        <v>12472300</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>25200</v>
+        <v>26880</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -17447,23 +17447,23 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
-        <v>9897000</v>
+        <v>8907300</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>24929</v>
+        <v>22437</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K267" s="5" t="n">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27164,7 +27164,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27638,9 +27638,9 @@
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
-$811万
-$23,181/呎
-(26年-05月-21日)</t>
+$842万
+$24,067/呎
+(26年-05月-09日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -27937,12 +27937,12 @@
 (26年-05月-29日)</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>J | 464呎 (3房)
-$1299万
-$28,000/呎
-(在售)</t>
+$1247万
+$26,880/呎
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -29148,7 +29148,7 @@
           <t>A | 512呎 (3房)
 $1200万
 $23,432/呎
-(26年-10月-12日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -29405,12 +29405,12 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 397呎 (3房)
-$990万
-$24,929/呎
-(在售)</t>
+$891万
+$22,437/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
